--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>91.56999999999999</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>104</v>
+        <v>103.09</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>92.59</v>
+        <v>91.11</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>105.23</v>
+        <v>104.13</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>99.19</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>109.7</v>
+        <v>110.41</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>101.71</v>
+        <v>102.06</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>112.5</v>
+        <v>113.07</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>83.66</v>
+        <v>84.08</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>91.89</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>86.53</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>95.03</v>
+        <v>95.31999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>88.56999999999999</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>97.98999999999999</v>
+        <v>98.97</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>95.86</v>
+        <v>96.77</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>106.14</v>
+        <v>107.01</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>81.25</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>88.93000000000001</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>95.29000000000001</v>
+        <v>93.37</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>104.27</v>
+        <v>102.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Mar 2026</t>
+          <t>Data through: Apr 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5780,18 +5780,38 @@
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>88.23999999999999</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>88.52</v>
+        <v>90.94</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>88.23999999999999</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>88.52</v>
+        <v>90.94</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="F253" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5804,7 +5824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10598,20 +10618,39 @@
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>88.23999999999999</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>88.52</v>
+        <v>90.94</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>88.23999999999999</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>88.52</v>
+        <v>90.94</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="D253" s="5" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="E253" s="5" t="n">
+        <v>85.3</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B252">
+  <conditionalFormatting sqref="B2:B253">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -10623,7 +10662,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C252">
+  <conditionalFormatting sqref="C2:C253">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -10635,7 +10674,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D252">
+  <conditionalFormatting sqref="D2:D253">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10647,7 +10686,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E252">
+  <conditionalFormatting sqref="E2:E253">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/TAS_historical_prices.xlsx
+++ b/outputs/TAS_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>90.29000000000001</v>
+        <v>90.53</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>103.09</v>
+        <v>103.26</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>91.11</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>104.13</v>
+        <v>105.42</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>99.68000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>110.41</v>
+        <v>110.5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>102.06</v>
+        <v>103.43</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>113.07</v>
+        <v>114.56</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>84.08</v>
+        <v>84.16</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>92.34999999999999</v>
+        <v>92.41</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>86.79000000000001</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>95.31999999999999</v>
+        <v>96.59</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>89.56999999999999</v>
+        <v>89.62</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>98.97</v>
+        <v>99</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>96.77</v>
+        <v>98.08</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>107.01</v>
+        <v>108.45</v>
       </c>
     </row>
     <row r="9">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>79.98999999999999</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>87.68000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>93.37</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>102.37</v>
+        <v>103.76</v>
       </c>
     </row>
     <row r="11">
@@ -690,10 +690,10 @@
         <v>392.08</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>537.86</v>
+        <v>545.26</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>687.21</v>
+        <v>696.66</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>86.38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>137.54</v>
+        <v>139.44</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>151.1</v>
+        <v>153.18</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>115.44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>195.86</v>
+        <v>198.56</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>201.27</v>
+        <v>204.04</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>141.07</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>186.29</v>
+        <v>188.85</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>245.14</v>
+        <v>248.52</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>78.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>120.12</v>
+        <v>121.77</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>135.2</v>
+        <v>137.06</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>102.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>142.44</v>
+        <v>144.4</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>176.81</v>
+        <v>179.25</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>59.27</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>99.48999999999999</v>
+        <v>100.86</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>102.3</v>
+        <v>103.71</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>73.78</v>
+        <v>74.8</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>80.98999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>40.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>63.4</v>
+        <v>64.27</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>69.36</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>35.76</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>55.58</v>
+        <v>56.34</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>61.27</v>
+        <v>62.11</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>32.55</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>48.52</v>
+        <v>49.19</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>55.61</v>
+        <v>56.37</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>33.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>56.69</v>
+        <v>57.47</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>57.51</v>
+        <v>58.3</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>47.58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.07</v>
+        <v>57.86</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>80.44</v>
+        <v>81.55</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>51.97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>69.61</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>88.61</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>68.81</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>80.89</v>
+        <v>82</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>115.38</v>
+        <v>116.97</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>39.83</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>58.8</v>
+        <v>59.61</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>66.59</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>41.53</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>63.76</v>
+        <v>64.64</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>69.23</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>36.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57.08</v>
+        <v>57.87</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>61.42</v>
+        <v>62.26</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>44.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>74.81999999999999</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>41.08</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>58.7</v>
+        <v>59.5</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>68.56</v>
+        <v>69.5</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>47.25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>73.91</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>78.84</v>
+        <v>79.92</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>88.31999999999999</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>112.76</v>
+        <v>114.31</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>53.83</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>84.63</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>89.76000000000001</v>
+        <v>91</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>82.19</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>121.37</v>
+        <v>123.04</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>136.5</v>
+        <v>138.37</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>72.31</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>109.73</v>
+        <v>111.24</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>119.6</v>
+        <v>121.25</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>79.93000000000001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>128.18</v>
+        <v>129.94</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>131.67</v>
+        <v>133.48</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>115.5</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>163.45</v>
+        <v>165.7</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>189.83</v>
+        <v>192.44</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>48.82</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>80.05</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>50.3</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>77.29000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>82.29000000000001</v>
+        <v>83.42</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>38.54</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>55.5</v>
+        <v>56.26</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>62.86</v>
+        <v>63.72</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>49.43</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>80.37</v>
+        <v>81.48</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>60.54</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>98.13</v>
+        <v>99.48</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>59.06</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>76.38</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>95.31</v>
+        <v>96.62</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>67.75</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>90.70999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>108.85</v>
+        <v>110.34</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>89.84</v>
+        <v>91.08</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>110.03</v>
+        <v>111.54</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>63.84</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>87.44</v>
+        <v>88.64</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>101.62</v>
+        <v>103.02</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>69.72</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>107.31</v>
+        <v>108.79</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>110.45</v>
+        <v>111.97</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>63.27</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>88.23</v>
+        <v>89.44</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>99.75</v>
+        <v>101.12</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>30.26</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>47.68</v>
+        <v>48.34</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>47.52</v>
+        <v>48.18</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>60.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>85.98</v>
+        <v>87.17</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>95.34</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>53.5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>68.48</v>
+        <v>69.42</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>83.38</v>
+        <v>84.53</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>56.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>71.64</v>
+        <v>72.63</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>87.87</v>
+        <v>89.08</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>61.31</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>79.19</v>
+        <v>80.28</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>95.76000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>38.3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>51.46</v>
+        <v>52.17</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>59.89</v>
+        <v>60.71</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>119.63</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>123.29</v>
+        <v>124.99</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>186.98</v>
+        <v>189.56</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>63.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>61.06</v>
+        <v>61.9</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>99.86</v>
+        <v>101.23</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>43.73</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>56.98</v>
+        <v>57.76</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>68.3</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>63.23</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>108.07</v>
+        <v>109.56</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>98.59</v>
+        <v>99.95</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>50.07</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>72.92</v>
+        <v>73.92</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>77.94</v>
+        <v>79.02</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>292.02</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>270.11</v>
+        <v>273.83</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>453.84</v>
+        <v>460.08</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>31.68</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>40.11</v>
+        <v>40.66</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>49.08</v>
+        <v>49.76</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>28.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>32.88</v>
+        <v>33.33</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.29</v>
+        <v>43.89</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>27.51</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33.13</v>
+        <v>33.59</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42.35</v>
+        <v>42.94</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>30.14</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>39.62</v>
+        <v>40.16</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>46.32</v>
+        <v>46.96</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>38.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>51.7</v>
+        <v>52.41</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>58.46</v>
+        <v>59.27</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>31.86</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>48.79</v>
+        <v>49.46</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>48.79</v>
+        <v>49.46</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>32.52</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>44.62</v>
+        <v>45.24</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>49.65</v>
+        <v>50.33</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>20.61</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>36.47</v>
+        <v>36.97</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.37</v>
+        <v>31.8</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>28.67</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>39.75</v>
+        <v>40.3</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>26.2</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>36.98</v>
+        <v>37.49</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>39.67</v>
+        <v>40.22</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>40.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>86.09</v>
+        <v>87.27</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>61.25</v>
+        <v>62.09</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>34.48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>46.59</v>
+        <v>47.23</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52</v>
+        <v>52.72</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>33.99</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>45.44</v>
+        <v>46.06</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.14</v>
+        <v>51.84</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>27.77</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>97.26000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>41.68</v>
+        <v>42.25</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>23.94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>31.08</v>
+        <v>31.51</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>35.85</v>
+        <v>36.34</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>18.56</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27.13</v>
+        <v>27.5</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>27.75</v>
+        <v>28.14</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>38.48</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>40.47</v>
+        <v>41.03</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>57.47</v>
+        <v>58.26</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>17.8</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>24.91</v>
+        <v>25.25</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>26.55</v>
+        <v>26.91</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>28.36</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>38.51</v>
+        <v>39.04</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.08</v>
+        <v>42.66</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>31.48</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>42.4</v>
+        <v>42.98</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>46.47</v>
+        <v>47.11</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>27.22</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>37.94</v>
+        <v>38.46</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>39.98</v>
+        <v>40.53</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>27.79</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>39.24</v>
+        <v>39.78</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>40.69</v>
+        <v>41.25</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>40.73</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>56.45</v>
+        <v>57.23</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>59.46</v>
+        <v>60.28</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>32.31</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>42.44</v>
+        <v>43.02</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.02</v>
+        <v>47.67</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>49.12</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>47.34</v>
+        <v>47.99</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>71.34999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>34.69</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.37</v>
+        <v>39.91</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.29</v>
+        <v>50.98</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>29.9</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>38.2</v>
+        <v>38.72</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>43.26</v>
+        <v>43.85</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>31.6</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.14</v>
+        <v>47.78</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.72</v>
+        <v>46.35</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>30.44</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>44.49</v>
+        <v>45.1</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.04</v>
+        <v>44.65</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>26.57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>37.4</v>
+        <v>37.91</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>38.44</v>
+        <v>38.97</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>34.13</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>56.88</v>
+        <v>57.66</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>49.37</v>
+        <v>50.05</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>29.92</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>54.05</v>
+        <v>54.79</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.27</v>
+        <v>43.87</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>29.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>51.94</v>
+        <v>52.65</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>43.15</v>
+        <v>43.74</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>42.04</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>51.91</v>
+        <v>52.62</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>60.68</v>
+        <v>61.52</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>29.9</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>47.41</v>
+        <v>48.06</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.08</v>
+        <v>43.68</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>38.55</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>49.54</v>
+        <v>50.22</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>55.45</v>
+        <v>56.22</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>67.45</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>84.81999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>96.59</v>
+        <v>97.92</v>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
@@ -2434,10 +2434,10 @@
         <v>48.6</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>67.31</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>69.28</v>
+        <v>70.23</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         <v>41.42</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>56</v>
+        <v>56.77</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>58.78</v>
+        <v>59.59</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
@@ -2482,10 +2482,10 @@
         <v>44.97</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>61.85</v>
+        <v>62.7</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>63.77</v>
+        <v>64.64</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         <v>51.39</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>71.66</v>
+        <v>72.64</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>72.81</v>
+        <v>73.81</v>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
@@ -2530,10 +2530,10 @@
         <v>46.41</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>66.11</v>
+        <v>67.02</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>65.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         <v>46.53</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>80.54000000000001</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>65.79000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         <v>46.11</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>64.67</v>
+        <v>65.56</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>65.12</v>
+        <v>66.02</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -2602,10 +2602,10 @@
         <v>50.82</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>70.27</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>71.7</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         <v>46.73</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>63.57</v>
+        <v>64.45</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>65.84</v>
+        <v>66.75</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         <v>49.68</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>62.86</v>
+        <v>63.72</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>69.91</v>
+        <v>70.87</v>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
@@ -2674,10 +2674,10 @@
         <v>51.77</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>70.12</v>
+        <v>71.08</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>72.76000000000001</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         <v>50.69</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>72.09</v>
+        <v>73.08</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>70.95</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         <v>49.44</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>63.95</v>
+        <v>64.83</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>68.92</v>
+        <v>69.87</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
@@ -2746,10 +2746,10 @@
         <v>44.8</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>58.91</v>
+        <v>59.72</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>62.21</v>
+        <v>63.06</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         <v>41.47</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>53.47</v>
+        <v>54.2</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>57.44</v>
+        <v>58.23</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         <v>52.99</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>65.06999999999999</v>
+        <v>65.97</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>73.23</v>
+        <v>74.23</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         <v>37.58</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>51.83</v>
+        <v>52.55</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>51.81</v>
+        <v>52.52</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -2842,10 +2842,10 @@
         <v>29.48</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>47.99</v>
+        <v>48.65</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>40.56</v>
+        <v>41.12</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         <v>43.27</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>60.27</v>
+        <v>61.1</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>59.42</v>
+        <v>60.23</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
         <v>45.47</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>61.37</v>
+        <v>62.21</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>62.32</v>
+        <v>63.17</v>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
@@ -2914,10 +2914,10 @@
         <v>38.57</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>51.55</v>
+        <v>52.26</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>52.77</v>
+        <v>53.5</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         <v>40.99</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>49.88</v>
+        <v>50.57</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>55.99</v>
+        <v>56.76</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         <v>44.06</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>58.84</v>
+        <v>59.65</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>60.08</v>
+        <v>60.91</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         <v>37.29</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>46.07</v>
+        <v>46.7</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>50.78</v>
+        <v>51.48</v>
       </c>
       <c r="F112" s="7" t="inlineStr"/>
     </row>
@@ -3006,10 +3006,10 @@
         <v>41.88</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>49.41</v>
+        <v>50.09</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>56.95</v>
+        <v>57.73</v>
       </c>
       <c r="F113" s="7" t="inlineStr"/>
     </row>
@@ -3026,10 +3026,10 @@
         <v>40.3</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>51.12</v>
+        <v>51.83</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>54.72</v>
+        <v>55.48</v>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
     </row>
@@ -3046,10 +3046,10 @@
         <v>32.91</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>47.37</v>
+        <v>48.03</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>44.66</v>
+        <v>45.27</v>
       </c>
       <c r="F115" s="7" t="inlineStr"/>
     </row>
@@ -3066,10 +3066,10 @@
         <v>37.03</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>54.17</v>
+        <v>54.91</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>50.22</v>
+        <v>50.91</v>
       </c>
       <c r="F116" s="7" t="inlineStr"/>
     </row>
@@ -3086,10 +3086,10 @@
         <v>44.4</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>61.34</v>
+        <v>62.19</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>60.18</v>
+        <v>61</v>
       </c>
       <c r="F117" s="7" t="inlineStr"/>
     </row>
@@ -3106,10 +3106,10 @@
         <v>36.8</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>47.51</v>
+        <v>48.17</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>49.84</v>
+        <v>50.53</v>
       </c>
       <c r="F118" s="7" t="inlineStr"/>
     </row>
@@ -3126,10 +3126,10 @@
         <v>41.1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>57.58</v>
+        <v>58.37</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>55.63</v>
+        <v>56.4</v>
       </c>
       <c r="F119" s="7" t="inlineStr"/>
     </row>
@@ -3146,10 +3146,10 @@
         <v>39.98</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>53.8</v>
+        <v>54.54</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>54.08</v>
+        <v>54.83</v>
       </c>
       <c r="F120" s="7" t="inlineStr"/>
     </row>
@@ -3166,10 +3166,10 @@
         <v>38.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>54.85</v>
+        <v>55.6</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>51.78</v>
+        <v>52.49</v>
       </c>
       <c r="F121" s="7" t="inlineStr"/>
     </row>
@@ -3186,10 +3186,10 @@
         <v>37.02</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>38.1</v>
+        <v>38.63</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>49.84</v>
+        <v>50.53</v>
       </c>
       <c r="F122" s="7" t="inlineStr"/>
     </row>
@@ -3206,10 +3206,10 @@
         <v>37.68</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>43.32</v>
+        <v>43.91</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>50.61</v>
+        <v>51.31</v>
       </c>
       <c r="F123" s="7" t="inlineStr"/>
     </row>
@@ -3226,10 +3226,10 @@
         <v>39.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>46.82</v>
+        <v>47.46</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>52.46</v>
+        <v>53.18</v>
       </c>
       <c r="F124" s="7" t="inlineStr"/>
     </row>
@@ -3246,10 +3246,10 @@
         <v>38.28</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>42.72</v>
+        <v>43.31</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>51.28</v>
+        <v>51.99</v>
       </c>
       <c r="F125" s="7" t="inlineStr"/>
     </row>
@@ -3266,10 +3266,10 @@
         <v>48.78</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>61.57</v>
+        <v>62.42</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>65.27</v>
+        <v>66.16</v>
       </c>
       <c r="F126" s="7" t="inlineStr"/>
     </row>
@@ -3286,10 +3286,10 @@
         <v>60.34</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>79.13</v>
+        <v>80.22</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>80.63</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F127" s="7" t="inlineStr"/>
     </row>
@@ -3306,10 +3306,10 @@
         <v>85.88</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>111.74</v>
+        <v>113.28</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>114.61</v>
+        <v>116.18</v>
       </c>
       <c r="F128" s="7" t="inlineStr"/>
     </row>
@@ -3326,10 +3326,10 @@
         <v>97.17</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>128.08</v>
+        <v>129.84</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>129.51</v>
+        <v>131.29</v>
       </c>
       <c r="F129" s="7" t="inlineStr"/>
     </row>
@@ -3346,10 +3346,10 @@
         <v>114.3</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>150.35</v>
+        <v>152.41</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>152.44</v>
+        <v>154.54</v>
       </c>
       <c r="F130" s="7" t="inlineStr"/>
     </row>
@@ -3366,10 +3366,10 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>221.1</v>
+        <v>224.14</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>218.87</v>
+        <v>221.88</v>
       </c>
       <c r="F131" s="7" t="inlineStr"/>
     </row>
@@ -3386,10 +3386,10 @@
         <v>256.22</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>337.03</v>
+        <v>341.67</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>342.17</v>
+        <v>346.88</v>
       </c>
       <c r="F132" s="7" t="inlineStr"/>
     </row>
@@ -3406,10 +3406,10 @@
         <v>236.68</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>315.84</v>
+        <v>320.19</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>315.62</v>
+        <v>319.96</v>
       </c>
       <c r="F133" s="7" t="inlineStr"/>
     </row>
@@ -3426,10 +3426,10 @@
         <v>57.34</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>60.52</v>
+        <v>61.35</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>100.06</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>97.72</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>133.04</v>
+        <v>134.87</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>97.12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>90.09999999999999</v>
+        <v>91.34</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>128.83</v>
+        <v>130.6</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>58.34</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>57.81</v>
+        <v>58.6</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>77.20999999999999</v>
+        <v>78.27</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>52.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>60.97</v>
+        <v>61.81</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>69.67</v>
+        <v>70.63</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>42.16</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>43.79</v>
+        <v>44.39</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>55.57</v>
+        <v>56.33</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>52.68</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>49.45</v>
+        <v>50.13</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>69.31</v>
+        <v>70.27</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>46.61</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>54.24</v>
+        <v>54.99</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>61.22</v>
+        <v>62.06</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>91.34999999999999</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>112.93</v>
+        <v>114.48</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>119.8</v>
+        <v>121.45</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>104.02</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>123.58</v>
+        <v>125.28</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>136.21</v>
+        <v>138.08</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>117.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>148.8</v>
+        <v>150.85</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>153.78</v>
+        <v>155.9</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>128.93</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>171.49</v>
+        <v>173.85</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>168.46</v>
+        <v>170.78</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>118.62</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>140.94</v>
+        <v>142.88</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>154.89</v>
+        <v>157.02</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>109.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>135.5</v>
+        <v>137.36</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>143.24</v>
+        <v>145.21</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>126.14</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>151.1</v>
+        <v>153.18</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>164.26</v>
+        <v>166.52</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>110.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>126.33</v>
+        <v>128.07</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>144.18</v>
+        <v>146.16</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>82.05</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>95.43000000000001</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>106.42</v>
+        <v>107.88</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>75.56</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>97.78</v>
+        <v>99.12</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>105.59</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>121.41</v>
+        <v>123.08</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>136.34</v>
+        <v>138.21</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>106.82</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>117.18</v>
+        <v>118.8</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>137.62</v>
+        <v>139.51</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>95.51000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>127.32</v>
+        <v>129.07</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>122.87</v>
+        <v>124.56</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>89.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>114.67</v>
+        <v>116.25</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>114.78</v>
+        <v>116.35</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>86.02</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>107.13</v>
+        <v>108.6</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>110.34</v>
+        <v>111.86</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>80.12</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>103.4</v>
+        <v>104.83</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>102.65</v>
+        <v>104.06</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>79.66</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>97.97</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>101.94</v>
+        <v>103.34</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>81.06</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>94.06</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>103.6</v>
+        <v>105.03</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>50.01</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>57.24</v>
+        <v>58.03</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>63.83</v>
+        <v>64.7</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>31.66</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>31.9</v>
+        <v>32.34</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>40.35</v>
+        <v>40.9</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>75.48</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>77.45</v>
+        <v>78.52</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>96.06</v>
+        <v>97.38</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>102.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>121.16</v>
+        <v>122.83</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>129.99</v>
+        <v>131.78</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>88.54000000000001</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>108.56</v>
+        <v>110.05</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>112.29</v>
+        <v>113.83</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>91.31999999999999</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>90.12</v>
+        <v>91.36</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>163.88</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>187.27</v>
+        <v>189.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>207.49</v>
+        <v>210.34</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>133.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>170.66</v>
+        <v>173.01</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>169.27</v>
+        <v>171.6</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>115.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>156.29</v>
+        <v>158.44</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>146.35</v>
+        <v>148.36</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>109.29</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>132.33</v>
+        <v>134.15</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>138.11</v>
+        <v>140.01</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>102.33</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>116.72</v>
+        <v>118.33</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>129.06</v>
+        <v>130.83</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>109.49</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>121.84</v>
+        <v>123.52</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>137.82</v>
+        <v>139.71</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>89.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>93.94</v>
+        <v>95.23</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>112.8</v>
+        <v>114.35</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>81.81</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>87.83</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>102.59</v>
+        <v>104</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>63.98</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>72.12</v>
+        <v>73.11</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>80.08</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>106.88</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>134.47</v>
+        <v>136.32</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>133.47</v>
+        <v>135.31</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>77.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>85.09</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>96.64</v>
+        <v>97.97</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>50.23</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>64.87</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>62.44</v>
+        <v>63.3</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>49.85</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>61.89</v>
+        <v>62.74</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>38.9</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>48.49</v>
+        <v>49.15</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>48.24</v>
+        <v>48.9</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>35.52</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>46.28</v>
+        <v>46.92</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>43.99</v>
+        <v>44.6</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>24.48</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>29.13</v>
+        <v>29.53</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>30.51</v>
+        <v>30.93</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>41.19</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>43.62</v>
+        <v>44.22</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>51.68</v>
+        <v>52.39</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>39.42</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>45.98</v>
+        <v>46.61</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>49.78</v>
+        <v>50.47</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>57.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>71.11</v>
+        <v>72.09</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>72.3</v>
+        <v>73.3</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>56.78</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>69.68000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>70.97</v>
+        <v>71.95</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>39.19</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>46.66</v>
+        <v>47.3</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>48.74</v>
+        <v>49.41</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>42.32</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>51.47</v>
+        <v>52.17</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>52.47</v>
+        <v>53.19</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>57.44</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>73.39</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>71</v>
+        <v>71.98</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>43.49</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>45.43</v>
+        <v>46.05</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>53.6</v>
+        <v>54.34</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>40.16</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>46.51</v>
+        <v>47.15</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>49.4</v>
+        <v>50.08</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>36.94</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>39.27</v>
+        <v>39.81</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>45.35</v>
+        <v>45.98</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>31.99</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>37.72</v>
+        <v>38.24</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.2</v>
+        <v>39.74</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>28.96</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>30.97</v>
+        <v>31.4</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>35.4</v>
+        <v>35.89</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>45.01</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>50.3</v>
+        <v>50.99</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>54.89</v>
+        <v>55.64</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>77.88</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>83.79000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>94.73999999999999</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>43.06</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>46.28</v>
+        <v>46.91</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>52.23</v>
+        <v>52.95</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>25.45</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>25.96</v>
+        <v>26.32</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>30.78</v>
+        <v>31.21</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>22.15</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>19.93</v>
+        <v>20.2</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>26.72</v>
+        <v>27.08</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>9.77</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>11.27</v>
+        <v>11.42</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.73</v>
+        <v>11.9</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>33.57</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>37.99</v>
+        <v>38.51</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.15</v>
+        <v>40.7</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>50.76</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>59.37</v>
+        <v>60.19</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>60.46</v>
+        <v>61.29</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>66.84999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>73.95</v>
+        <v>74.97</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>79.05</v>
+        <v>80.14</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>78.13</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>84.78</v>
+        <v>85.95</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>91.73</v>
+        <v>93</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>78.79000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>87.23999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>91.86</v>
+        <v>93.12</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>165</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>163.72</v>
+        <v>165.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>191.22</v>
+        <v>193.85</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>241.96</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>250.22</v>
+        <v>253.66</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>278.76</v>
+        <v>282.59</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>382.49</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>328.43</v>
+        <v>332.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>438.08</v>
+        <v>444.11</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>366.3</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>367.51</v>
+        <v>372.56</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>416.98</v>
+        <v>422.72</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>169.69</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>169.17</v>
+        <v>171.49</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>192</v>
+        <v>194.64</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>150.78</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>149.29</v>
+        <v>151.34</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>169.58</v>
+        <v>171.91</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>126.75</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>136.37</v>
+        <v>138.24</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>141.68</v>
+        <v>143.63</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>114.81</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>112.19</v>
+        <v>113.73</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>127.55</v>
+        <v>129.3</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>67.38</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>84.31999999999999</v>
+        <v>85.48</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>81.12</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>95.48</v>
+        <v>96.8</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>89.17</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>76.66</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>89.22</v>
+        <v>90.45</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>83.89</v>
+        <v>85.05</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>68.13</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.91</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>74.23</v>
+        <v>75.25</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>70.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>76.08</v>
+        <v>77.13</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>77.08</v>
+        <v>78.14</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>86.54000000000001</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>91.17</v>
+        <v>92.42</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>93.75</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>52.33</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>41.09</v>
+        <v>41.66</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>56.53</v>
+        <v>57.31</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>32.72</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>25.09</v>
+        <v>25.44</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.21</v>
+        <v>35.69</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>37.93</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>40.36</v>
+        <v>40.92</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>40.66</v>
+        <v>41.22</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>24.88</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>28.52</v>
+        <v>28.92</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>26.57</v>
+        <v>26.94</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>36.02</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>40.13</v>
+        <v>40.69</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>38.39</v>
+        <v>38.91</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>57.48</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>63.78</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>61.13</v>
+        <v>61.97</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>49.05</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>55.28</v>
+        <v>56.04</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.05</v>
+        <v>52.77</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>49.55</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>53.03</v>
+        <v>53.75</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>52.42</v>
+        <v>53.14</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>110.19</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>86.34</v>
+        <v>87.53</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>116.22</v>
+        <v>117.82</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>67.51000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>73.23</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>70.98</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>70.58</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>76.86</v>
+        <v>77.91</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>73.95</v>
+        <v>74.97</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>145.64</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>147.26</v>
+        <v>149.28</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>152.07</v>
+        <v>154.16</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>212.93</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>185.48</v>
+        <v>188.03</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>221.57</v>
+        <v>224.61</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>215.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>187.95</v>
+        <v>190.54</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>224.21</v>
+        <v>227.3</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>156.24</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>133.71</v>
+        <v>135.55</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>162.34</v>
+        <v>164.57</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>31.25</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>23.37</v>
+        <v>23.69</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>32.45</v>
+        <v>32.89</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>52.52</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>51.67</v>
+        <v>52.38</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>54.5</v>
+        <v>55.25</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>96.58</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>99.40000000000001</v>
+        <v>100.77</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>100.15</v>
+        <v>101.52</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>68.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>78.87</v>
+        <v>79.95</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>70.95999999999999</v>
+        <v>71.94</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>109.08</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>117.39</v>
+        <v>119</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>112.69</v>
+        <v>114.24</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>125.01</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>125.33</v>
+        <v>127.06</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>128.75</v>
+        <v>130.52</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>100.83</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>102.72</v>
+        <v>104.14</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>103.53</v>
+        <v>104.96</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>98.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>102.97</v>
+        <v>104.39</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>100.97</v>
+        <v>102.36</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>113.37</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>105.64</v>
+        <v>107.09</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>115.83</v>
+        <v>117.43</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>327.99</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>223.55</v>
+        <v>226.63</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>334.29</v>
+        <v>338.89</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>130.45</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>119.59</v>
+        <v>121.23</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>132.37</v>
+        <v>134.19</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>133.56</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>126.51</v>
+        <v>128.25</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>134.94</v>
+        <v>136.79</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>36.24</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>36.45</v>
+        <v>36.96</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>26.88</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>24.65</v>
+        <v>24.99</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>26.99</v>
+        <v>27.36</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>34.34</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>40.59</v>
+        <v>41.15</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>34.41</v>
+        <v>34.88</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>55.6</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>59.34</v>
+        <v>60.16</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>55.6</v>
+        <v>56.36</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>114.88</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>100.93</v>
+        <v>101.85</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>114.88</v>
+        <v>115.93</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>87.56</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.28</v>
+        <v>90.69</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.56</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>82.45</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>85.3</v>
+        <v>87.34</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>82.45</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>85.3</v>
+        <v>87.34</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5874,10 +5874,10 @@
         <v>392.08</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>537.86</v>
+        <v>545.26</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>687.21</v>
+        <v>696.66</v>
       </c>
     </row>
     <row r="3">
@@ -5893,10 +5893,10 @@
         <v>86.38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>137.54</v>
+        <v>139.44</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>151.1</v>
+        <v>153.18</v>
       </c>
     </row>
     <row r="4">
@@ -5912,10 +5912,10 @@
         <v>115.44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>195.86</v>
+        <v>198.56</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>201.27</v>
+        <v>204.04</v>
       </c>
     </row>
     <row r="5">
@@ -5931,10 +5931,10 @@
         <v>141.07</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>186.29</v>
+        <v>188.85</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>245.14</v>
+        <v>248.52</v>
       </c>
     </row>
     <row r="6">
@@ -5950,10 +5950,10 @@
         <v>78.06</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>120.12</v>
+        <v>121.77</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>135.2</v>
+        <v>137.06</v>
       </c>
     </row>
     <row r="7">
@@ -5969,10 +5969,10 @@
         <v>102.26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>142.44</v>
+        <v>144.4</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>176.81</v>
+        <v>179.25</v>
       </c>
     </row>
     <row r="8">
@@ -5988,10 +5988,10 @@
         <v>59.27</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>99.48999999999999</v>
+        <v>100.86</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>102.3</v>
+        <v>103.71</v>
       </c>
     </row>
     <row r="9">
@@ -6007,10 +6007,10 @@
         <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>73.78</v>
+        <v>74.8</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>80.98999999999999</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -6026,10 +6026,10 @@
         <v>40.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>63.4</v>
+        <v>64.27</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>69.36</v>
+        <v>70.31999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6045,10 +6045,10 @@
         <v>35.76</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>55.58</v>
+        <v>56.34</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>61.27</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="12">
@@ -6064,10 +6064,10 @@
         <v>32.55</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>48.52</v>
+        <v>49.19</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>55.61</v>
+        <v>56.37</v>
       </c>
     </row>
     <row r="13">
@@ -6083,10 +6083,10 @@
         <v>33.84</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>56.69</v>
+        <v>57.47</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>57.51</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="14">
@@ -6102,10 +6102,10 @@
         <v>47.58</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>57.07</v>
+        <v>57.86</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>80.44</v>
+        <v>81.55</v>
       </c>
     </row>
     <row r="15">
@@ -6121,10 +6121,10 @@
         <v>51.97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>69.61</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>88.61</v>
       </c>
     </row>
     <row r="16">
@@ -6140,10 +6140,10 @@
         <v>68.81</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>80.89</v>
+        <v>82</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>115.38</v>
+        <v>116.97</v>
       </c>
     </row>
     <row r="17">
@@ -6159,10 +6159,10 @@
         <v>39.83</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>58.8</v>
+        <v>59.61</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>66.59</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -6178,10 +6178,10 @@
         <v>41.53</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>63.76</v>
+        <v>64.64</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>69.23</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -6197,10 +6197,10 @@
         <v>36.83</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>57.08</v>
+        <v>57.87</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>61.42</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="20">
@@ -6216,10 +6216,10 @@
         <v>44.85</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>66.40000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>74.81999999999999</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -6235,10 +6235,10 @@
         <v>41.08</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>58.7</v>
+        <v>59.5</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>68.56</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="22">
@@ -6254,10 +6254,10 @@
         <v>47.25</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>73.91</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>78.84</v>
+        <v>79.92</v>
       </c>
     </row>
     <row r="23">
@@ -6273,10 +6273,10 @@
         <v>67.59999999999999</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>88.31999999999999</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>112.76</v>
+        <v>114.31</v>
       </c>
     </row>
     <row r="24">
@@ -6292,10 +6292,10 @@
         <v>53.83</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>84.63</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>89.76000000000001</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
@@ -6311,10 +6311,10 @@
         <v>82.19</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>121.37</v>
+        <v>123.04</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>136.5</v>
+        <v>138.37</v>
       </c>
     </row>
     <row r="26">
@@ -6330,10 +6330,10 @@
         <v>72.31</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>109.73</v>
+        <v>111.24</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>119.6</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="27">
@@ -6349,10 +6349,10 @@
         <v>79.93000000000001</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>128.18</v>
+        <v>129.94</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>131.67</v>
+        <v>133.48</v>
       </c>
     </row>
     <row r="28">
@@ -6368,10 +6368,10 @@
         <v>115.5</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>163.45</v>
+        <v>165.7</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>189.83</v>
+        <v>192.44</v>
       </c>
     </row>
     <row r="29">
@@ -6387,10 +6387,10 @@
         <v>48.82</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>66.73999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>80.05</v>
+        <v>81.15000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -6406,10 +6406,10 @@
         <v>50.3</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>77.29000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>82.29000000000001</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="31">
@@ -6425,10 +6425,10 @@
         <v>38.54</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>55.5</v>
+        <v>56.26</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>62.86</v>
+        <v>63.72</v>
       </c>
     </row>
     <row r="32">
@@ -6444,10 +6444,10 @@
         <v>49.43</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>72.73999999999999</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>80.37</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="33">
@@ -6463,10 +6463,10 @@
         <v>60.54</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>98.13</v>
+        <v>99.48</v>
       </c>
     </row>
     <row r="34">
@@ -6482,10 +6482,10 @@
         <v>59.06</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>76.38</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>95.31</v>
+        <v>96.62</v>
       </c>
     </row>
     <row r="35">
@@ -6501,10 +6501,10 @@
         <v>67.75</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>90.70999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>108.85</v>
+        <v>110.34</v>
       </c>
     </row>
     <row r="36">
@@ -6520,10 +6520,10 @@
         <v>68.79000000000001</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>89.84</v>
+        <v>91.08</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>110.03</v>
+        <v>111.54</v>
       </c>
     </row>
     <row r="37">
@@ -6539,10 +6539,10 @@
         <v>63.84</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>87.44</v>
+        <v>88.64</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>101.62</v>
+        <v>103.02</v>
       </c>
     </row>
     <row r="38">
@@ -6558,10 +6558,10 @@
         <v>69.72</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>107.31</v>
+        <v>108.79</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>110.45</v>
+        <v>111.97</v>
       </c>
     </row>
     <row r="39">
@@ -6577,10 +6577,10 @@
         <v>63.27</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>88.23</v>
+        <v>89.44</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>99.75</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="40">
@@ -6596,10 +6596,10 @@
         <v>30.26</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>47.68</v>
+        <v>48.34</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>47.52</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="41">
@@ -6615,10 +6615,10 @@
         <v>60.94</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>85.98</v>
+        <v>87.17</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>95.34</v>
+        <v>96.65000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -6634,10 +6634,10 @@
         <v>53.5</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>68.48</v>
+        <v>69.42</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>83.38</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="43">
@@ -6653,10 +6653,10 @@
         <v>56.32</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>71.64</v>
+        <v>72.63</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>87.87</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="44">
@@ -6672,10 +6672,10 @@
         <v>61.31</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>79.19</v>
+        <v>80.28</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>95.76000000000001</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="45">
@@ -6691,10 +6691,10 @@
         <v>38.3</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>51.46</v>
+        <v>52.17</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>59.89</v>
+        <v>60.71</v>
       </c>
     </row>
     <row r="46">
@@ -6710,10 +6710,10 @@
         <v>119.63</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>123.29</v>
+        <v>124.99</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>186.98</v>
+        <v>189.56</v>
       </c>
     </row>
     <row r="47">
@@ -6729,10 +6729,10 @@
         <v>63.91</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>61.06</v>
+        <v>61.9</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>99.86</v>
+        <v>101.23</v>
       </c>
     </row>
     <row r="48">
@@ -6748,10 +6748,10 @@
         <v>43.73</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>56.98</v>
+        <v>57.76</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>68.3</v>
+        <v>69.23999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -6767,10 +6767,10 @@
         <v>63.23</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>108.07</v>
+        <v>109.56</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>98.59</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="50">
@@ -6786,10 +6786,10 @@
         <v>50.07</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>72.92</v>
+        <v>73.92</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>77.94</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="51">
@@ -6805,10 +6805,10 @@
         <v>292.02</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>270.11</v>
+        <v>273.83</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>453.84</v>
+        <v>460.08</v>
       </c>
     </row>
     <row r="52">
@@ -6824,10 +6824,10 @@
         <v>31.68</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>40.11</v>
+        <v>40.66</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>49.08</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="53">
@@ -6843,10 +6843,10 @@
         <v>28.03</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>32.88</v>
+        <v>33.33</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>43.29</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="54">
@@ -6862,10 +6862,10 @@
         <v>27.51</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>33.13</v>
+        <v>33.59</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>42.35</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="55">
@@ -6881,10 +6881,10 @@
         <v>30.14</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>39.62</v>
+        <v>40.16</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>46.32</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="56">
@@ -6900,10 +6900,10 @@
         <v>38.11</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>51.7</v>
+        <v>52.41</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>58.46</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="57">
@@ -6919,10 +6919,10 @@
         <v>31.86</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>48.79</v>
+        <v>49.46</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>48.79</v>
+        <v>49.46</v>
       </c>
     </row>
     <row r="58">
@@ -6938,10 +6938,10 @@
         <v>32.52</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>44.62</v>
+        <v>45.24</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>49.65</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="59">
@@ -6957,10 +6957,10 @@
         <v>20.61</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>36.47</v>
+        <v>36.97</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>31.37</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="60">
@@ -6976,10 +6976,10 @@
         <v>28.67</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>39.75</v>
+        <v>40.3</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="61">
@@ -6995,10 +6995,10 @@
         <v>26.2</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>36.98</v>
+        <v>37.49</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>39.67</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="62">
@@ -7014,10 +7014,10 @@
         <v>40.53</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>86.09</v>
+        <v>87.27</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>61.25</v>
+        <v>62.09</v>
       </c>
     </row>
     <row r="63">
@@ -7033,10 +7033,10 @@
         <v>34.48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>46.59</v>
+        <v>47.23</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>52</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="64">
@@ -7052,10 +7052,10 @@
         <v>33.99</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>45.44</v>
+        <v>46.06</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>51.14</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="65">
@@ -7071,10 +7071,10 @@
         <v>27.77</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>97.26000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>41.68</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="66">
@@ -7090,10 +7090,10 @@
         <v>23.94</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>31.08</v>
+        <v>31.51</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>35.85</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="67">
@@ -7109,10 +7109,10 @@
         <v>18.56</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>27.13</v>
+        <v>27.5</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>27.75</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="68">
@@ -7128,10 +7128,10 @@
         <v>38.48</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>40.47</v>
+        <v>41.03</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>57.47</v>
+        <v>58.26</v>
       </c>
     </row>
     <row r="69">
@@ -7147,10 +7147,10 @@
         <v>17.8</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>24.91</v>
+        <v>25.25</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>26.55</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="70">
@@ -7166,10 +7166,10 @@
         <v>28.36</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>38.51</v>
+        <v>39.04</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>42.08</v>
+        <v>42.66</v>
       </c>
     </row>
     <row r="71">
@@ -7185,10 +7185,10 @@
         <v>31.48</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>42.4</v>
+        <v>42.98</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>46.47</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="72">
@@ -7204,10 +7204,10 @@
         <v>27.22</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>37.94</v>
+        <v>38.46</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>39.98</v>
+        <v>40.53</v>
       </c>
     </row>
     <row r="73">
@@ -7223,10 +7223,10 @@
         <v>27.79</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>39.24</v>
+        <v>39.78</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>40.69</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="74">
@@ -7242,10 +7242,10 @@
         <v>40.73</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>56.45</v>
+        <v>57.23</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>59.46</v>
+        <v>60.28</v>
       </c>
     </row>
     <row r="75">
@@ -7261,10 +7261,10 @@
         <v>32.31</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>42.44</v>
+        <v>43.02</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>47.02</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="76">
@@ -7280,10 +7280,10 @@
         <v>49.12</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>47.34</v>
+        <v>47.99</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>71.34999999999999</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="77">
@@ -7299,10 +7299,10 @@
         <v>34.69</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>39.37</v>
+        <v>39.91</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>50.29</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="78">
@@ -7318,10 +7318,10 @@
         <v>29.9</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>38.2</v>
+        <v>38.72</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>43.26</v>
+        <v>43.85</v>
       </c>
     </row>
     <row r="79">
@@ -7337,10 +7337,10 @@
         <v>31.6</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>47.14</v>
+        <v>47.78</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.72</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="80">
@@ -7356,10 +7356,10 @@
         <v>30.44</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>44.49</v>
+        <v>45.1</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>44.04</v>
+        <v>44.65</v>
       </c>
     </row>
     <row r="81">
@@ -7375,10 +7375,10 @@
         <v>26.57</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>37.4</v>
+        <v>37.91</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>38.44</v>
+        <v>38.97</v>
       </c>
     </row>
     <row r="82">
@@ -7394,10 +7394,10 @@
         <v>34.13</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>56.88</v>
+        <v>57.66</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>49.37</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="83">
@@ -7413,10 +7413,10 @@
         <v>29.92</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>54.05</v>
+        <v>54.79</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>43.27</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="84">
@@ -7432,10 +7432,10 @@
         <v>29.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>51.94</v>
+        <v>52.65</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>43.15</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="85">
@@ -7451,10 +7451,10 @@
         <v>42.04</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>51.91</v>
+        <v>52.62</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>60.68</v>
+        <v>61.52</v>
       </c>
     </row>
     <row r="86">
@@ -7470,10 +7470,10 @@
         <v>29.9</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>47.41</v>
+        <v>48.06</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>43.08</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="87">
@@ -7489,10 +7489,10 @@
         <v>38.55</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>49.54</v>
+        <v>50.22</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>55.45</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="88">
@@ -7508,10 +7508,10 @@
         <v>67.45</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>84.81999999999999</v>
+        <v>85.98</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>96.59</v>
+        <v>97.92</v>
       </c>
     </row>
     <row r="89">
@@ -7527,10 +7527,10 @@
         <v>48.6</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>67.31</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>69.28</v>
+        <v>70.23</v>
       </c>
     </row>
     <row r="90">
@@ -7546,10 +7546,10 @@
         <v>41.42</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>56</v>
+        <v>56.77</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>58.78</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="91">
@@ -7565,10 +7565,10 @@
         <v>44.97</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>61.85</v>
+        <v>62.7</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>63.77</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="92">
@@ -7584,10 +7584,10 @@
         <v>51.39</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>71.66</v>
+        <v>72.64</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>72.81</v>
+        <v>73.81</v>
       </c>
     </row>
     <row r="93">
@@ -7603,10 +7603,10 @@
         <v>46.41</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>66.11</v>
+        <v>67.02</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>65.7</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -7622,10 +7622,10 @@
         <v>46.53</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>80.54000000000001</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>65.79000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="95">
@@ -7641,10 +7641,10 @@
         <v>46.11</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>64.67</v>
+        <v>65.56</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>65.12</v>
+        <v>66.02</v>
       </c>
     </row>
     <row r="96">
@@ -7660,10 +7660,10 @@
         <v>50.82</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>70.27</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>71.7</v>
+        <v>72.68000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -7679,10 +7679,10 @@
         <v>46.73</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>63.57</v>
+        <v>64.45</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>65.84</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="98">
@@ -7698,10 +7698,10 @@
         <v>49.68</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>62.86</v>
+        <v>63.72</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>69.91</v>
+        <v>70.87</v>
       </c>
     </row>
     <row r="99">
@@ -7717,10 +7717,10 @@
         <v>51.77</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>70.12</v>
+        <v>71.08</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>72.76000000000001</v>
+        <v>73.76000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -7736,10 +7736,10 @@
         <v>50.69</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>72.09</v>
+        <v>73.08</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>70.95</v>
+        <v>71.93000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7755,10 +7755,10 @@
         <v>49.44</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>63.95</v>
+        <v>64.83</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>68.92</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="102">
@@ -7774,10 +7774,10 @@
         <v>44.8</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>58.91</v>
+        <v>59.72</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>62.21</v>
+        <v>63.06</v>
       </c>
     </row>
     <row r="103">
@@ -7793,10 +7793,10 @@
         <v>41.47</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>53.47</v>
+        <v>54.2</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>57.44</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="104">
@@ -7812,10 +7812,10 @@
         <v>52.99</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>65.06999999999999</v>
+        <v>65.97</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>73.23</v>
+        <v>74.23</v>
       </c>
     </row>
     <row r="105">
@@ -7831,10 +7831,10 @@
         <v>37.58</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>51.83</v>
+        <v>52.55</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>51.81</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="106">
@@ -7850,10 +7850,10 @@
         <v>29.48</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>47.99</v>
+        <v>48.65</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>40.56</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="107">
@@ -7869,10 +7869,10 @@
         <v>43.27</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>60.27</v>
+        <v>61.1</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>59.42</v>
+        <v>60.23</v>
       </c>
     </row>
     <row r="108">
@@ -7888,10 +7888,10 @@
         <v>45.47</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>61.37</v>
+        <v>62.21</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>62.32</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="109">
@@ -7907,10 +7907,10 @@
         <v>38.57</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>51.55</v>
+        <v>52.26</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>52.77</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="110">
@@ -7926,10 +7926,10 @@
         <v>40.99</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>49.88</v>
+        <v>50.57</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>55.99</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="111">
@@ -7945,10 +7945,10 @@
         <v>44.06</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>58.84</v>
+        <v>59.65</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>60.08</v>
+        <v>60.91</v>
       </c>
     </row>
     <row r="112">
@@ -7964,10 +7964,10 @@
         <v>37.29</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>46.07</v>
+        <v>46.7</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>50.78</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="113">
@@ -7983,10 +7983,10 @@
         <v>41.88</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>49.41</v>
+        <v>50.09</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>56.95</v>
+        <v>57.73</v>
       </c>
     </row>
     <row r="114">
@@ -8002,10 +8002,10 @@
         <v>40.3</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>51.12</v>
+        <v>51.83</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>54.72</v>
+        <v>55.48</v>
       </c>
     </row>
     <row r="115">
@@ -8021,10 +8021,10 @@
         <v>32.91</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>47.37</v>
+        <v>48.03</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>44.66</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="116">
@@ -8040,10 +8040,10 @@
         <v>37.03</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>54.17</v>
+        <v>54.91</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>50.22</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="117">
@@ -8059,10 +8059,10 @@
         <v>44.4</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>61.34</v>
+        <v>62.19</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>60.18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118">
@@ -8078,10 +8078,10 @@
         <v>36.8</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>47.51</v>
+        <v>48.17</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>49.84</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="119">
@@ -8097,10 +8097,10 @@
         <v>41.1</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>57.58</v>
+        <v>58.37</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>55.63</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="120">
@@ -8116,10 +8116,10 @@
         <v>39.98</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>53.8</v>
+        <v>54.54</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>54.08</v>
+        <v>54.83</v>
       </c>
     </row>
     <row r="121">
@@ -8135,10 +8135,10 @@
         <v>38.37</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>54.85</v>
+        <v>55.6</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>51.78</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="122">
@@ -8154,10 +8154,10 @@
         <v>37.02</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>38.1</v>
+        <v>38.63</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>49.84</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="123">
@@ -8173,10 +8173,10 @@
         <v>37.68</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>43.32</v>
+        <v>43.91</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>50.61</v>
+        <v>51.31</v>
       </c>
     </row>
     <row r="124">
@@ -8192,10 +8192,10 @@
         <v>39.11</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>46.82</v>
+        <v>47.46</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>52.46</v>
+        <v>53.18</v>
       </c>
     </row>
     <row r="125">
@@ -8211,10 +8211,10 @@
         <v>38.28</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>42.72</v>
+        <v>43.31</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>51.28</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="126">
@@ -8230,10 +8230,10 @@
         <v>48.78</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>61.57</v>
+        <v>62.42</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>65.27</v>
+        <v>66.16</v>
       </c>
     </row>
     <row r="127">
@@ -8249,10 +8249,10 @@
         <v>60.34</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>79.13</v>
+        <v>80.22</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>80.63</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -8268,10 +8268,10 @@
         <v>85.88</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>111.74</v>
+        <v>113.28</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>114.61</v>
+        <v>116.18</v>
       </c>
     </row>
     <row r="129">
@@ -8287,10 +8287,10 @@
         <v>97.17</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>128.08</v>
+        <v>129.84</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>129.51</v>
+        <v>131.29</v>
       </c>
     </row>
     <row r="130">
@@ -8306,10 +8306,10 @@
         <v>114.3</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>150.35</v>
+        <v>152.41</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>152.44</v>
+        <v>154.54</v>
       </c>
     </row>
     <row r="131">
@@ -8325,10 +8325,10 @@
         <v>164</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>221.1</v>
+        <v>224.14</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>218.87</v>
+        <v>221.88</v>
       </c>
     </row>
     <row r="132">
@@ -8344,10 +8344,10 @@
         <v>256.22</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>337.03</v>
+        <v>341.67</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>342.17</v>
+        <v>346.88</v>
       </c>
     </row>
     <row r="133">
@@ -8363,10 +8363,10 @@
         <v>236.68</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>315.84</v>
+        <v>320.19</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>315.62</v>
+        <v>319.96</v>
       </c>
     </row>
     <row r="134">
@@ -8382,10 +8382,10 @@
         <v>57.34</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>60.52</v>
+        <v>61.35</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -8401,10 +8401,10 @@
         <v>100.06</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>96.40000000000001</v>
+        <v>97.72</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>133.04</v>
+        <v>134.87</v>
       </c>
     </row>
     <row r="136">
@@ -8420,10 +8420,10 @@
         <v>97.12</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>90.09999999999999</v>
+        <v>91.34</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>128.83</v>
+        <v>130.6</v>
       </c>
     </row>
     <row r="137">
@@ -8439,10 +8439,10 @@
         <v>58.34</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>57.81</v>
+        <v>58.6</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>77.20999999999999</v>
+        <v>78.27</v>
       </c>
     </row>
     <row r="138">
@@ -8458,10 +8458,10 @@
         <v>52.77</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>60.97</v>
+        <v>61.81</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>69.67</v>
+        <v>70.63</v>
       </c>
     </row>
     <row r="139">
@@ -8477,10 +8477,10 @@
         <v>42.16</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>43.79</v>
+        <v>44.39</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>55.57</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="140">
@@ -8496,10 +8496,10 @@
         <v>52.68</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>49.45</v>
+        <v>50.13</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>69.31</v>
+        <v>70.27</v>
       </c>
     </row>
     <row r="141">
@@ -8515,10 +8515,10 @@
         <v>46.61</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>54.24</v>
+        <v>54.99</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>61.22</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="142">
@@ -8534,10 +8534,10 @@
         <v>91.34999999999999</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>112.93</v>
+        <v>114.48</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>119.8</v>
+        <v>121.45</v>
       </c>
     </row>
     <row r="143">
@@ -8553,10 +8553,10 @@
         <v>104.02</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>123.58</v>
+        <v>125.28</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>136.21</v>
+        <v>138.08</v>
       </c>
     </row>
     <row r="144">
@@ -8572,10 +8572,10 @@
         <v>117.62</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>148.8</v>
+        <v>150.85</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>153.78</v>
+        <v>155.9</v>
       </c>
     </row>
     <row r="145">
@@ -8591,10 +8591,10 @@
         <v>128.93</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>171.49</v>
+        <v>173.85</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>168.46</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="146">
@@ -8610,10 +8610,10 @@
         <v>118.62</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>140.94</v>
+        <v>142.88</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>154.89</v>
+        <v>157.02</v>
       </c>
     </row>
     <row r="147">
@@ -8629,10 +8629,10 @@
         <v>109.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>135.5</v>
+        <v>137.36</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>143.24</v>
+        <v>145.21</v>
       </c>
     </row>
     <row r="148">
@@ -8648,10 +8648,10 @@
         <v>126.14</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>151.1</v>
+        <v>153.18</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>164.26</v>
+        <v>166.52</v>
       </c>
     </row>
     <row r="149">
@@ -8667,10 +8667,10 @@
         <v>110.94</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>126.33</v>
+        <v>128.07</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>144.18</v>
+        <v>146.16</v>
       </c>
     </row>
     <row r="150">
@@ -8686,10 +8686,10 @@
         <v>82.05</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>95.43000000000001</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>106.42</v>
+        <v>107.88</v>
       </c>
     </row>
     <row r="151">
@@ -8705,10 +8705,10 @@
         <v>75.56</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>88.84999999999999</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>97.78</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="152">
@@ -8724,10 +8724,10 @@
         <v>105.59</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>121.41</v>
+        <v>123.08</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>136.34</v>
+        <v>138.21</v>
       </c>
     </row>
     <row r="153">
@@ -8743,10 +8743,10 @@
         <v>106.82</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>117.18</v>
+        <v>118.8</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>137.62</v>
+        <v>139.51</v>
       </c>
     </row>
     <row r="154">
@@ -8762,10 +8762,10 @@
         <v>95.51000000000001</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>127.32</v>
+        <v>129.07</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>122.87</v>
+        <v>124.56</v>
       </c>
     </row>
     <row r="155">
@@ -8781,10 +8781,10 @@
         <v>89.34999999999999</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>114.67</v>
+        <v>116.25</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>114.78</v>
+        <v>116.35</v>
       </c>
     </row>
     <row r="156">
@@ -8800,10 +8800,10 @@
         <v>86.02</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>107.13</v>
+        <v>108.6</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>110.34</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="157">
@@ -8819,10 +8819,10 @@
         <v>80.12</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>103.4</v>
+        <v>104.83</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>102.65</v>
+        <v>104.06</v>
       </c>
     </row>
     <row r="158">
@@ -8838,10 +8838,10 @@
         <v>79.66</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>97.97</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>101.94</v>
+        <v>103.34</v>
       </c>
     </row>
     <row r="159">
@@ -8857,10 +8857,10 @@
         <v>81.06</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>94.06</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>103.6</v>
+        <v>105.03</v>
       </c>
     </row>
     <row r="160">
@@ -8876,10 +8876,10 @@
         <v>50.01</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>57.24</v>
+        <v>58.03</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>63.83</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="161">
@@ -8895,10 +8895,10 @@
         <v>31.66</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>31.9</v>
+        <v>32.34</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>40.35</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="162">
@@ -8914,10 +8914,10 @@
         <v>75.48</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>77.45</v>
+        <v>78.52</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>96.06</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="163">
@@ -8933,10 +8933,10 @@
         <v>102.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>121.16</v>
+        <v>122.83</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>129.99</v>
+        <v>131.78</v>
       </c>
     </row>
     <row r="164">
@@ -8952,10 +8952,10 @@
         <v>88.54000000000001</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>108.56</v>
+        <v>110.05</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>112.29</v>
+        <v>113.83</v>
       </c>
     </row>
     <row r="165">
@@ -8971,10 +8971,10 @@
         <v>71.18000000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>91.31999999999999</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>90.12</v>
+        <v>91.36</v>
       </c>
     </row>
     <row r="166">
@@ -8990,10 +8990,10 @@
         <v>163.88</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>187.27</v>
+        <v>189.84</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>207.49</v>
+        <v>210.34</v>
       </c>
     </row>
     <row r="167">
@@ -9009,10 +9009,10 @@
         <v>133.69</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>170.66</v>
+        <v>173.01</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>169.27</v>
+        <v>171.6</v>
       </c>
     </row>
     <row r="168">
@@ -9028,10 +9028,10 @@
         <v>115.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>156.29</v>
+        <v>158.44</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>146.35</v>
+        <v>148.36</v>
       </c>
     </row>
     <row r="169">
@@ -9047,10 +9047,10 @@
         <v>109.29</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>132.33</v>
+        <v>134.15</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>138.11</v>
+        <v>140.01</v>
       </c>
     </row>
     <row r="170">
@@ -9066,10 +9066,10 @@
         <v>102.33</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>116.72</v>
+        <v>118.33</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>129.06</v>
+        <v>130.83</v>
       </c>
     </row>
     <row r="171">
@@ -9085,10 +9085,10 @@
         <v>109.49</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>121.84</v>
+        <v>123.52</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>137.82</v>
+        <v>139.71</v>
       </c>
     </row>
     <row r="172">
@@ -9104,10 +9104,10 @@
         <v>89.78</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>93.94</v>
+        <v>95.23</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>112.8</v>
+        <v>114.35</v>
       </c>
     </row>
     <row r="173">
@@ -9123,10 +9123,10 @@
         <v>81.81</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>87.83</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>102.59</v>
+        <v>104</v>
       </c>
     </row>
     <row r="174">
@@ -9142,10 +9142,10 @@
         <v>63.98</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>72.12</v>
+        <v>73.11</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>80.08</v>
+        <v>81.18000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9161,10 +9161,10 @@
         <v>106.88</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>134.47</v>
+        <v>136.32</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>133.47</v>
+        <v>135.31</v>
       </c>
     </row>
     <row r="176">
@@ -9180,10 +9180,10 @@
         <v>77.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>85.09</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>96.64</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="177">
@@ -9199,10 +9199,10 @@
         <v>50.23</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>64.87</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>62.44</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="178">
@@ -9218,10 +9218,10 @@
         <v>49.85</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>70.56999999999999</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>61.89</v>
+        <v>62.74</v>
       </c>
     </row>
     <row r="179">
@@ -9237,10 +9237,10 @@
         <v>38.9</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>48.49</v>
+        <v>49.15</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>48.24</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="180">
@@ -9256,10 +9256,10 @@
         <v>35.52</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>46.28</v>
+        <v>46.92</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>43.99</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="181">
@@ -9275,10 +9275,10 @@
         <v>24.48</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>29.13</v>
+        <v>29.53</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>30.51</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="182">
@@ -9294,10 +9294,10 @@
         <v>41.19</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>43.62</v>
+        <v>44.22</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>51.68</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="183">
@@ -9313,10 +9313,10 @@
         <v>39.42</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>45.98</v>
+        <v>46.61</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>49.78</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="184">
@@ -9332,10 +9332,10 @@
         <v>57.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>71.11</v>
+        <v>72.09</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>72.3</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="185">
@@ -9351,10 +9351,10 @@
         <v>56.78</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>69.68000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>70.97</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="186">
@@ -9370,10 +9370,10 @@
         <v>39.19</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>46.66</v>
+        <v>47.3</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>48.74</v>
+        <v>49.41</v>
       </c>
     </row>
     <row r="187">
@@ -9389,10 +9389,10 @@
         <v>42.32</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>51.47</v>
+        <v>52.17</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>52.47</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="188">
@@ -9408,10 +9408,10 @@
         <v>57.44</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>73.39</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>71</v>
+        <v>71.98</v>
       </c>
     </row>
     <row r="189">
@@ -9427,10 +9427,10 @@
         <v>43.49</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>45.43</v>
+        <v>46.05</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>53.6</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="190">
@@ -9446,10 +9446,10 @@
         <v>40.16</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>46.51</v>
+        <v>47.15</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>49.4</v>
+        <v>50.08</v>
       </c>
     </row>
     <row r="191">
@@ -9465,10 +9465,10 @@
         <v>36.94</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>39.27</v>
+        <v>39.81</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>45.35</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="192">
@@ -9484,10 +9484,10 @@
         <v>31.99</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>37.72</v>
+        <v>38.24</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>39.2</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="193">
@@ -9503,10 +9503,10 @@
         <v>28.96</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>30.97</v>
+        <v>31.4</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>35.4</v>
+        <v>35.89</v>
       </c>
     </row>
     <row r="194">
@@ -9522,10 +9522,10 @@
         <v>45.01</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>50.3</v>
+        <v>50.99</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>54.89</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="195">
@@ -9541,10 +9541,10 @@
         <v>77.88</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>83.79000000000001</v>
+        <v>84.94</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>94.73999999999999</v>
+        <v>96.04000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -9560,10 +9560,10 @@
         <v>43.06</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>46.28</v>
+        <v>46.91</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>52.23</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="197">
@@ -9579,10 +9579,10 @@
         <v>25.45</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>25.96</v>
+        <v>26.32</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>30.78</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="198">
@@ -9598,10 +9598,10 @@
         <v>22.15</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>19.93</v>
+        <v>20.2</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>26.72</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="199">
@@ -9617,10 +9617,10 @@
         <v>9.77</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>11.27</v>
+        <v>11.42</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>11.73</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="200">
@@ -9636,10 +9636,10 @@
         <v>33.57</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>37.99</v>
+        <v>38.51</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>40.15</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="201">
@@ -9655,10 +9655,10 @@
         <v>50.76</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>59.37</v>
+        <v>60.19</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>60.46</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="202">
@@ -9674,10 +9674,10 @@
         <v>66.84999999999999</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>73.95</v>
+        <v>74.97</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>79.05</v>
+        <v>80.14</v>
       </c>
     </row>
     <row r="203">
@@ -9693,10 +9693,10 @@
         <v>78.13</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>84.78</v>
+        <v>85.95</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>91.73</v>
+        <v>93</v>
       </c>
     </row>
     <row r="204">
@@ -9712,10 +9712,10 @@
         <v>78.79000000000001</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>87.23999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>91.86</v>
+        <v>93.12</v>
       </c>
     </row>
     <row r="205">
@@ -9731,10 +9731,10 @@
         <v>165</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>163.72</v>
+        <v>165.97</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>191.22</v>
+        <v>193.85</v>
       </c>
     </row>
     <row r="206">
@@ -9750,10 +9750,10 @@
         <v>241.96</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>250.22</v>
+        <v>253.66</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>278.76</v>
+        <v>282.59</v>
       </c>
     </row>
     <row r="207">
@@ -9769,10 +9769,10 @@
         <v>382.49</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>328.43</v>
+        <v>332.94</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>438.08</v>
+        <v>444.11</v>
       </c>
     </row>
     <row r="208">
@@ -9788,10 +9788,10 @@
         <v>366.3</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>367.51</v>
+        <v>372.56</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>416.98</v>
+        <v>422.72</v>
       </c>
     </row>
     <row r="209">
@@ -9807,10 +9807,10 @@
         <v>169.69</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>169.17</v>
+        <v>171.49</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>192</v>
+        <v>194.64</v>
       </c>
     </row>
     <row r="210">
@@ -9826,10 +9826,10 @@
         <v>150.78</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>149.29</v>
+        <v>151.34</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>169.58</v>
+        <v>171.91</v>
       </c>
     </row>
     <row r="211">
@@ -9845,10 +9845,10 @@
         <v>126.75</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>136.37</v>
+        <v>138.24</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>141.68</v>
+        <v>143.63</v>
       </c>
     </row>
     <row r="212">
@@ -9864,10 +9864,10 @@
         <v>114.81</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>112.19</v>
+        <v>113.73</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>127.55</v>
+        <v>129.3</v>
       </c>
     </row>
     <row r="213">
@@ -9883,10 +9883,10 @@
         <v>67.38</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>84.31999999999999</v>
+        <v>85.48</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>75.43000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -9902,10 +9902,10 @@
         <v>81.12</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>95.48</v>
+        <v>96.8</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>89.17</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="215">
@@ -9921,10 +9921,10 @@
         <v>76.66</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>89.22</v>
+        <v>90.45</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>83.89</v>
+        <v>85.05</v>
       </c>
     </row>
     <row r="216">
@@ -9940,10 +9940,10 @@
         <v>68.13</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>78.81999999999999</v>
+        <v>79.91</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>74.23</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="217">
@@ -9959,10 +9959,10 @@
         <v>70.95</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>76.08</v>
+        <v>77.13</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>77.08</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="218">
@@ -9978,10 +9978,10 @@
         <v>86.54000000000001</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>91.17</v>
+        <v>92.42</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>93.75</v>
+        <v>95.04000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -9997,10 +9997,10 @@
         <v>52.33</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>41.09</v>
+        <v>41.66</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>56.53</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="220">
@@ -10016,10 +10016,10 @@
         <v>32.72</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>25.09</v>
+        <v>25.44</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>35.21</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="221">
@@ -10035,10 +10035,10 @@
         <v>37.93</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>40.36</v>
+        <v>40.92</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>40.66</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="222">
@@ -10054,10 +10054,10 @@
         <v>24.88</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>28.52</v>
+        <v>28.92</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>26.57</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="223">
@@ -10073,10 +10073,10 @@
         <v>36.02</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>40.13</v>
+        <v>40.69</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>38.39</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="224">
@@ -10092,10 +10092,10 @@
         <v>57.48</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>63.78</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>61.13</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="225">
@@ -10111,10 +10111,10 @@
         <v>49.05</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>55.28</v>
+        <v>56.04</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.05</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="226">
@@ -10130,10 +10130,10 @@
         <v>49.55</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>53.03</v>
+        <v>53.75</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>52.42</v>
+        <v>53.14</v>
       </c>
     </row>
     <row r="227">
@@ -10149,10 +10149,10 @@
         <v>110.19</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>86.34</v>
+        <v>87.53</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>116.22</v>
+        <v>117.82</v>
       </c>
     </row>
     <row r="228">
@@ -10168,10 +10168,10 @@
         <v>67.51000000000001</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>73.23</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>70.98</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -10187,10 +10187,10 @@
         <v>70.58</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>76.86</v>
+        <v>77.91</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>73.95</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="230">
@@ -10206,10 +10206,10 @@
         <v>145.64</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>147.26</v>
+        <v>149.28</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>152.07</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="231">
@@ -10225,10 +10225,10 @@
         <v>212.93</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>185.48</v>
+        <v>188.03</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>221.57</v>
+        <v>224.61</v>
       </c>
     </row>
     <row r="232">
@@ -10244,10 +10244,10 @@
         <v>215.63</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>187.95</v>
+        <v>190.54</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>224.21</v>
+        <v>227.3</v>
       </c>
     </row>
     <row r="233">
@@ -10263,10 +10263,10 @@
         <v>156.24</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>133.71</v>
+        <v>135.55</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>162.34</v>
+        <v>164.57</v>
       </c>
     </row>
     <row r="234">
@@ -10282,10 +10282,10 @@
         <v>31.25</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>23.37</v>
+        <v>23.69</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>32.45</v>
+        <v>32.89</v>
       </c>
     </row>
     <row r="235">
@@ -10301,10 +10301,10 @@
         <v>52.52</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>51.67</v>
+        <v>52.38</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>54.5</v>
+        <v>55.25</v>
       </c>
     </row>
     <row r="236">
@@ -10320,10 +10320,10 @@
         <v>96.58</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>99.40000000000001</v>
+        <v>100.77</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>100.15</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="237">
@@ -10339,10 +10339,10 @@
         <v>68.48</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>78.87</v>
+        <v>79.95</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>70.95999999999999</v>
+        <v>71.94</v>
       </c>
     </row>
     <row r="238">
@@ -10358,10 +10358,10 @@
         <v>109.08</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>117.39</v>
+        <v>119</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>112.69</v>
+        <v>114.24</v>
       </c>
     </row>
     <row r="239">
@@ -10377,10 +10377,10 @@
         <v>125.01</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>125.33</v>
+        <v>127.06</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>128.75</v>
+        <v>130.52</v>
       </c>
     </row>
     <row r="240">
@@ -10396,10 +10396,10 @@
         <v>100.83</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>102.72</v>
+        <v>104.14</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>103.53</v>
+        <v>104.96</v>
       </c>
     </row>
     <row r="241">
@@ -10415,10 +10415,10 @@
         <v>98.58</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>102.97</v>
+        <v>104.39</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>100.97</v>
+        <v>102.36</v>
       </c>
     </row>
     <row r="242">
@@ -10434,10 +10434,10 @@
         <v>113.37</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>105.64</v>
+        <v>107.09</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>115.83</v>
+        <v>117.43</v>
       </c>
     </row>
     <row r="243">
@@ -10453,10 +10453,10 @@
         <v>327.99</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>223.55</v>
+        <v>226.63</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>334.29</v>
+        <v>338.89</v>
       </c>
     </row>
     <row r="244">
@@ -10472,10 +10472,10 @@
         <v>130.45</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>119.59</v>
+        <v>121.23</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>132.37</v>
+        <v>134.19</v>
       </c>
     </row>
     <row r="245">
@@ -10491,10 +10491,10 @@
         <v>133.56</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>126.51</v>
+        <v>128.25</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>134.94</v>
+        <v>136.79</v>
       </c>
     </row>
     <row r="246">
@@ -10510,10 +10510,10 @@
         <v>36.24</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>28.8</v>
+        <v>29.2</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>36.45</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="247">
@@ -10529,10 +10529,10 @@
         <v>26.88</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>24.65</v>
+        <v>24.99</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>26.99</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="248">
@@ -10548,10 +10548,10 @@
         <v>34.34</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>40.59</v>
+        <v>41.15</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>34.41</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="249">
@@ -10567,10 +10567,10 @@
         <v>55.6</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>59.34</v>
+        <v>60.16</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>55.6</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="250">
@@ -10586,10 +10586,10 @@
         <v>114.88</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>100.93</v>
+        <v>101.85</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>114.88</v>
+        <v>115.93</v>
       </c>
     </row>
     <row r="251">
@@ -10605,10 +10605,10 @@
         <v>87.56</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>90.28</v>
+        <v>90.69</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.56</v>
+        <v>87.95999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -10637,16 +10637,16 @@
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>82.45</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>85.3</v>
+        <v>87.34</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>82.45</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>85.3</v>
+        <v>87.34</v>
       </c>
     </row>
   </sheetData>
